--- a/objectifs.xlsx
+++ b/objectifs.xlsx
@@ -1,161 +1,91 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sogelink-my.sharepoint.com/personal/mathilde_panier_sogelink_com/Documents/KPI/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="63" documentId="11_AB4BD737D3447C4EE959F89456B7467E35C5CC79" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3E0710BA-4F0A-4725-B360-A36A2656E145}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="2" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Budget" sheetId="1" r:id="rId1"/>
-    <sheet name="LE1" sheetId="2" r:id="rId2"/>
-    <sheet name="LE2" sheetId="3" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Budget" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LE1" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LE2" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ObjectifsEquipe" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="20">
-  <si>
-    <t>Objectifs CA mensuels — à compléter par solution</t>
-  </si>
-  <si>
-    <t>Valeurs en euros (€) — SHERPA inclus dans LITTERALIS</t>
-  </si>
-  <si>
-    <t>Mois</t>
-  </si>
-  <si>
-    <t>Global (€)</t>
-  </si>
-  <si>
-    <t>LITTERALIS (€)</t>
-  </si>
-  <si>
-    <t>GEODP (€)</t>
-  </si>
-  <si>
-    <t>Janvier</t>
-  </si>
-  <si>
-    <t>Février</t>
-  </si>
-  <si>
-    <t>Mars</t>
-  </si>
-  <si>
-    <t>Avril</t>
-  </si>
-  <si>
-    <t>Mai</t>
-  </si>
-  <si>
-    <t>Juin</t>
-  </si>
-  <si>
-    <t>Juillet</t>
-  </si>
-  <si>
-    <t>Août</t>
-  </si>
-  <si>
-    <t>Septembre</t>
-  </si>
-  <si>
-    <t>Octobre</t>
-  </si>
-  <si>
-    <t>Novembre</t>
-  </si>
-  <si>
-    <t>Décembre</t>
-  </si>
-  <si>
-    <t>TOTAL</t>
-  </si>
-  <si>
-    <t>💡 Le script lit la ligne du mois courant automatiquement.</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;€&quot;"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="11">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="FF1F3864"/>
       <sz val="13"/>
-      <color rgb="FF1F3864"/>
-      <name val="Calibri"/>
     </font>
     <font>
-      <i/>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="FF595959"/>
       <sz val="10"/>
-      <color rgb="FF595959"/>
-      <name val="Calibri"/>
     </font>
     <font>
-      <b/>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
     </font>
     <font>
+      <name val="Calibri"/>
+      <color rgb="FF000000"/>
       <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
     </font>
     <font>
+      <name val="Calibri"/>
+      <color rgb="FF0000FF"/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="Calibri"/>
     </font>
     <font>
-      <b/>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="FF000000"/>
       <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
     </font>
     <font>
-      <i/>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="FF767676"/>
       <sz val="9"/>
-      <color rgb="FF767676"/>
-      <name val="Calibri"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001F4E79"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001F4E79"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -196,6 +126,11 @@
         <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F4E79"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -224,58 +159,120 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+  <cellXfs count="18">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -563,226 +560,270 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:D19"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="16" customWidth="1"/>
-    <col min="2" max="4" width="20" customWidth="1"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" s="5">
+    <row r="1" ht="21.95" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Objectifs CA mensuels — à compléter par solution</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Valeurs en euros (€) — SHERPA inclus dans LITTERALIS</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Mois</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Global (€)</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>LITTERALIS (€)</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>GEODP (€)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Janvier</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
         <v>140830</v>
       </c>
-      <c r="C5" s="5">
+      <c r="C5" s="5" t="n">
         <v>86170</v>
       </c>
-      <c r="D5" s="5">
+      <c r="D5" s="5" t="n">
         <v>54660</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6" s="7">
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Février</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="n">
         <v>107440</v>
       </c>
-      <c r="C6" s="7">
+      <c r="C6" s="7" t="n">
         <v>64620</v>
       </c>
-      <c r="D6" s="7">
+      <c r="D6" s="7" t="n">
         <v>42820</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" s="5">
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Mars</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
         <v>104660</v>
       </c>
-      <c r="C7" s="5">
+      <c r="C7" s="5" t="n">
         <v>70950</v>
       </c>
-      <c r="D7" s="5">
+      <c r="D7" s="5" t="n">
         <v>33710</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8" s="7">
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>Avril</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="n">
         <v>104280</v>
       </c>
-      <c r="C8" s="7">
+      <c r="C8" s="7" t="n">
         <v>68750</v>
       </c>
-      <c r="D8" s="7">
+      <c r="D8" s="7" t="n">
         <v>35530</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B9" s="5">
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Mai</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
         <v>91630</v>
       </c>
-      <c r="C9" s="5">
+      <c r="C9" s="5" t="n">
         <v>52460</v>
       </c>
-      <c r="D9" s="5">
+      <c r="D9" s="5" t="n">
         <v>39170</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="B10" s="7">
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>Juin</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="n">
         <v>120460</v>
       </c>
-      <c r="C10" s="7">
+      <c r="C10" s="7" t="n">
         <v>63980</v>
       </c>
-      <c r="D10" s="7">
+      <c r="D10" s="7" t="n">
         <v>56480</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B11" s="5">
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Juillet</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
         <v>125720</v>
       </c>
-      <c r="C11" s="5">
+      <c r="C11" s="5" t="n">
         <v>69240</v>
       </c>
-      <c r="D11" s="5">
+      <c r="D11" s="5" t="n">
         <v>56480</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="B12" s="7">
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>Août</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="n">
         <v>72150</v>
       </c>
-      <c r="C12" s="7">
+      <c r="C12" s="7" t="n">
         <v>44820</v>
       </c>
-      <c r="D12" s="7">
+      <c r="D12" s="7" t="n">
         <v>27330</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B13" s="5">
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Septembre</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
         <v>100850</v>
       </c>
-      <c r="C13" s="5">
+      <c r="C13" s="5" t="n">
         <v>74430</v>
       </c>
-      <c r="D13" s="5">
+      <c r="D13" s="5" t="n">
         <v>26420</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="B14" s="7">
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>Octobre</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="n">
         <v>103940</v>
       </c>
-      <c r="C14" s="7">
+      <c r="C14" s="7" t="n">
         <v>72960</v>
       </c>
-      <c r="D14" s="7">
+      <c r="D14" s="7" t="n">
         <v>30980</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B15" s="5">
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Novembre</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
         <v>127620</v>
       </c>
-      <c r="C15" s="5">
+      <c r="C15" s="5" t="n">
         <v>72960</v>
       </c>
-      <c r="D15" s="5">
+      <c r="D15" s="5" t="n">
         <v>54660</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="B16" s="7">
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>Décembre</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="n">
         <v>117170</v>
       </c>
-      <c r="C16" s="7">
+      <c r="C16" s="7" t="n">
         <v>63420</v>
       </c>
-      <c r="D16" s="7">
+      <c r="D16" s="7" t="n">
         <v>53750</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="8" t="s">
-        <v>18</v>
+    <row r="17">
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
       </c>
       <c r="B17" s="9">
         <f>SUM(B5:B16)</f>
-        <v>1316750</v>
+        <v/>
       </c>
       <c r="C17" s="9">
         <f>SUM(C5:C16)</f>
-        <v>804760</v>
+        <v/>
       </c>
       <c r="D17" s="9">
         <f>SUM(D5:D16)</f>
-        <v>511990</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="10" t="s">
-        <v>19</v>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="10" t="inlineStr">
+        <is>
+          <t>💡 Le script lit la ligne du mois courant automatiquement.</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -791,228 +832,272 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D83DFFE0-39DB-47EB-8790-C43D04D419B3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:D19"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="20.42578125" customWidth="1"/>
-    <col min="2" max="2" width="24.28515625" customWidth="1"/>
-    <col min="3" max="3" width="16.5703125" customWidth="1"/>
-    <col min="4" max="4" width="19.28515625" customWidth="1"/>
+    <col width="20.42578125" customWidth="1" min="1" max="1"/>
+    <col width="24.28515625" customWidth="1" min="2" max="2"/>
+    <col width="16.5703125" customWidth="1" min="3" max="3"/>
+    <col width="19.28515625" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" s="5">
+    <row r="1" ht="17.25" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Objectifs CA mensuels — à compléter par solution</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Valeurs en euros (€) — SHERPA inclus dans LITTERALIS</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Mois</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Global (€)</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>LITTERALIS (€)</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>GEODP (€)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Janvier</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
         <v>140830</v>
       </c>
-      <c r="C5" s="5">
+      <c r="C5" s="5" t="n">
         <v>86170</v>
       </c>
-      <c r="D5" s="5">
+      <c r="D5" s="5" t="n">
         <v>54660</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6" s="7">
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Février</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="n">
         <v>107440</v>
       </c>
-      <c r="C6" s="7">
+      <c r="C6" s="7" t="n">
         <v>64620</v>
       </c>
-      <c r="D6" s="7">
+      <c r="D6" s="7" t="n">
         <v>42820</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" s="5">
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Mars</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
         <v>104660</v>
       </c>
-      <c r="C7" s="5">
+      <c r="C7" s="5" t="n">
         <v>70950</v>
       </c>
-      <c r="D7" s="5">
+      <c r="D7" s="5" t="n">
         <v>33710</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8" s="7">
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>Avril</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="n">
         <v>104280</v>
       </c>
-      <c r="C8" s="7">
+      <c r="C8" s="7" t="n">
         <v>68750</v>
       </c>
-      <c r="D8" s="7">
+      <c r="D8" s="7" t="n">
         <v>35530</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="B9" s="12">
+    <row r="9">
+      <c r="A9" s="11" t="inlineStr">
+        <is>
+          <t>Mai</t>
+        </is>
+      </c>
+      <c r="B9" s="12" t="n">
         <v>80000</v>
       </c>
-      <c r="C9" s="12">
+      <c r="C9" s="12" t="n">
         <v>53000</v>
       </c>
-      <c r="D9" s="12">
+      <c r="D9" s="12" t="n">
         <v>27000</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="B10" s="14">
+    <row r="10">
+      <c r="A10" s="13" t="inlineStr">
+        <is>
+          <t>Juin</t>
+        </is>
+      </c>
+      <c r="B10" s="14" t="n">
         <v>90000</v>
       </c>
-      <c r="C10" s="14">
+      <c r="C10" s="14" t="n">
         <v>42000</v>
       </c>
-      <c r="D10" s="14">
+      <c r="D10" s="14" t="n">
         <v>48000</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="B11" s="12">
+    <row r="11">
+      <c r="A11" s="11" t="inlineStr">
+        <is>
+          <t>Juillet</t>
+        </is>
+      </c>
+      <c r="B11" s="12" t="n">
         <v>132000</v>
       </c>
-      <c r="C11" s="12">
+      <c r="C11" s="12" t="n">
         <v>74500</v>
       </c>
-      <c r="D11" s="12">
+      <c r="D11" s="12" t="n">
         <v>57500</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="B12" s="14">
+    <row r="12">
+      <c r="A12" s="13" t="inlineStr">
+        <is>
+          <t>Août</t>
+        </is>
+      </c>
+      <c r="B12" s="14" t="n">
         <v>80000</v>
       </c>
-      <c r="C12" s="14">
+      <c r="C12" s="14" t="n">
         <v>47171</v>
       </c>
-      <c r="D12" s="14">
+      <c r="D12" s="14" t="n">
         <v>32829</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="B13" s="12">
+    <row r="13">
+      <c r="A13" s="11" t="inlineStr">
+        <is>
+          <t>Septembre</t>
+        </is>
+      </c>
+      <c r="B13" s="12" t="n">
         <v>125750</v>
       </c>
-      <c r="C13" s="12">
+      <c r="C13" s="12" t="n">
         <v>78250</v>
       </c>
-      <c r="D13" s="12">
+      <c r="D13" s="12" t="n">
         <v>47500</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="B14" s="12">
+    <row r="14">
+      <c r="A14" s="13" t="inlineStr">
+        <is>
+          <t>Octobre</t>
+        </is>
+      </c>
+      <c r="B14" s="12" t="n">
         <v>125750</v>
       </c>
-      <c r="C14" s="14">
+      <c r="C14" s="14" t="n">
         <v>78250</v>
       </c>
-      <c r="D14" s="14">
+      <c r="D14" s="14" t="n">
         <v>47500</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="B15" s="12">
+    <row r="15">
+      <c r="A15" s="11" t="inlineStr">
+        <is>
+          <t>Novembre</t>
+        </is>
+      </c>
+      <c r="B15" s="12" t="n">
         <v>122750</v>
       </c>
-      <c r="C15" s="12">
+      <c r="C15" s="12" t="n">
         <v>63750</v>
       </c>
-      <c r="D15" s="12">
+      <c r="D15" s="12" t="n">
         <v>59000</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="B16" s="14">
+    <row r="16">
+      <c r="A16" s="13" t="inlineStr">
+        <is>
+          <t>Décembre</t>
+        </is>
+      </c>
+      <c r="B16" s="14" t="n">
         <v>115750</v>
       </c>
-      <c r="C16" s="14">
+      <c r="C16" s="14" t="n">
         <v>63750</v>
       </c>
-      <c r="D16" s="14">
+      <c r="D16" s="14" t="n">
         <v>52000</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="8" t="s">
-        <v>18</v>
+    <row r="17">
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
       </c>
       <c r="B17" s="9">
         <f>SUM(B5:B16)</f>
-        <v>1329210</v>
+        <v/>
       </c>
       <c r="C17" s="9">
         <f>SUM(C5:C16)</f>
-        <v>791161</v>
+        <v/>
       </c>
       <c r="D17" s="9">
         <f>SUM(D5:D16)</f>
-        <v>538049</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="10" t="s">
-        <v>19</v>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="10" t="inlineStr">
+        <is>
+          <t>💡 Le script lit la ligne du mois courant automatiquement.</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -1021,231 +1106,459 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77EAB4AF-1B19-4EDB-85FD-F4CB77B5666D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:D19"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
-    <col min="2" max="2" width="21.5703125" customWidth="1"/>
-    <col min="3" max="3" width="28.7109375" customWidth="1"/>
-    <col min="4" max="4" width="31.42578125" customWidth="1"/>
+    <col width="18.7109375" customWidth="1" min="1" max="1"/>
+    <col width="21.5703125" customWidth="1" min="2" max="2"/>
+    <col width="28.7109375" customWidth="1" min="3" max="3"/>
+    <col width="31.42578125" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" s="5">
+    <row r="1" ht="17.25" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Objectifs CA mensuels — à compléter par solution</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Valeurs en euros (€) — SHERPA inclus dans LITTERALIS</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Mois</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Global (€)</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>LITTERALIS (€)</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>GEODP (€)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Janvier</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
         <v>140830</v>
       </c>
-      <c r="C5" s="5">
+      <c r="C5" s="5" t="n">
         <v>86170</v>
       </c>
-      <c r="D5" s="5">
+      <c r="D5" s="5" t="n">
         <v>54660</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6" s="7">
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Février</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="n">
         <v>107440</v>
       </c>
-      <c r="C6" s="7">
+      <c r="C6" s="7" t="n">
         <v>64620</v>
       </c>
-      <c r="D6" s="7">
+      <c r="D6" s="7" t="n">
         <v>42820</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" s="5">
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Mars</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
         <v>104660</v>
       </c>
-      <c r="C7" s="5">
+      <c r="C7" s="5" t="n">
         <v>70950</v>
       </c>
-      <c r="D7" s="5">
+      <c r="D7" s="5" t="n">
         <v>33710</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8" s="7">
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>Avril</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="n">
         <v>104280</v>
       </c>
-      <c r="C8" s="7">
+      <c r="C8" s="7" t="n">
         <v>68750</v>
       </c>
-      <c r="D8" s="7">
+      <c r="D8" s="7" t="n">
         <v>35530</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B9" s="5">
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Mai</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
         <v>80000</v>
       </c>
-      <c r="C9" s="5">
+      <c r="C9" s="5" t="n">
         <v>53000</v>
       </c>
-      <c r="D9" s="5">
+      <c r="D9" s="5" t="n">
         <v>27000</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="B10" s="7">
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>Juin</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="n">
         <v>90000</v>
       </c>
-      <c r="C10" s="7">
+      <c r="C10" s="7" t="n">
         <v>42000</v>
       </c>
-      <c r="D10" s="7">
+      <c r="D10" s="7" t="n">
         <v>48000</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="B11" s="12">
+    <row r="11">
+      <c r="A11" s="11" t="inlineStr">
+        <is>
+          <t>Juillet</t>
+        </is>
+      </c>
+      <c r="B11" s="12" t="n">
         <v>95000</v>
       </c>
-      <c r="C11" s="12">
+      <c r="C11" s="12" t="n">
         <v>38000</v>
       </c>
-      <c r="D11" s="12">
+      <c r="D11" s="12" t="n">
         <v>57000</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="B12" s="14">
+    <row r="12">
+      <c r="A12" s="13" t="inlineStr">
+        <is>
+          <t>Août</t>
+        </is>
+      </c>
+      <c r="B12" s="14" t="n">
         <v>50000</v>
       </c>
-      <c r="C12" s="14">
+      <c r="C12" s="14" t="n">
         <v>21000</v>
       </c>
-      <c r="D12" s="14">
+      <c r="D12" s="14" t="n">
         <v>29000</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="B13" s="12">
+    <row r="13">
+      <c r="A13" s="11" t="inlineStr">
+        <is>
+          <t>Septembre</t>
+        </is>
+      </c>
+      <c r="B13" s="12" t="n">
         <v>106000</v>
       </c>
-      <c r="C13" s="12">
+      <c r="C13" s="12" t="n">
         <v>46000</v>
       </c>
-      <c r="D13" s="12">
+      <c r="D13" s="12" t="n">
         <v>60000</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="B14" s="12">
+    <row r="14">
+      <c r="A14" s="13" t="inlineStr">
+        <is>
+          <t>Octobre</t>
+        </is>
+      </c>
+      <c r="B14" s="12" t="n">
         <v>113000</v>
       </c>
-      <c r="C14" s="14">
+      <c r="C14" s="14" t="n">
         <v>62000</v>
       </c>
-      <c r="D14" s="14">
+      <c r="D14" s="14" t="n">
         <v>51000</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="B15" s="12">
+    <row r="15">
+      <c r="A15" s="11" t="inlineStr">
+        <is>
+          <t>Novembre</t>
+        </is>
+      </c>
+      <c r="B15" s="12" t="n">
         <v>128000</v>
       </c>
-      <c r="C15" s="12">
+      <c r="C15" s="12" t="n">
         <v>75000</v>
       </c>
-      <c r="D15" s="12">
+      <c r="D15" s="12" t="n">
         <v>53000</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="B16" s="14">
+    <row r="16">
+      <c r="A16" s="13" t="inlineStr">
+        <is>
+          <t>Décembre</t>
+        </is>
+      </c>
+      <c r="B16" s="14" t="n">
         <v>122000</v>
       </c>
-      <c r="C16" s="14">
+      <c r="C16" s="14" t="n">
         <v>71000</v>
       </c>
-      <c r="D16" s="14">
+      <c r="D16" s="14" t="n">
         <v>51000</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="8" t="s">
-        <v>18</v>
+    <row r="17">
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
       </c>
       <c r="B17" s="9">
         <f>SUM(B5:B16)</f>
-        <v>1241210</v>
+        <v/>
       </c>
       <c r="C17" s="9">
         <f>SUM(C5:C16)</f>
-        <v>698490</v>
+        <v/>
       </c>
       <c r="D17" s="9">
         <f>SUM(D5:D16)</f>
-        <v>542720</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="10" t="s">
-        <v>19</v>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="10" t="inlineStr">
+        <is>
+          <t>💡 Le script lit la ligne du mois courant automatiquement.</t>
+        </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="15" t="inlineStr">
+        <is>
+          <t>Objectifs d'équipe 2026 — révisable en cours d'année</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="16" t="inlineStr">
+        <is>
+          <t>OBJECTIF CA NON RÉCURRENT (Coordin)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="17" t="inlineStr">
+        <is>
+          <t>Palier</t>
+        </is>
+      </c>
+      <c r="B4" s="17" t="inlineStr">
+        <is>
+          <t>Seuil prime (%)</t>
+        </is>
+      </c>
+      <c r="C4" s="17" t="inlineStr">
+        <is>
+          <t>CA cible (€)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Déclencheur</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>80</v>
+      </c>
+      <c r="C5" t="n">
+        <v>1000000</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Palier 2</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>90</v>
+      </c>
+      <c r="C6" t="n">
+        <v>1200000</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>100</v>
+      </c>
+      <c r="C7" t="n">
+        <v>1300000</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="16" t="inlineStr">
+        <is>
+          <t>OBJECTIF RÉDUCTION BACKLOG REWORK</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="17" t="inlineStr">
+        <is>
+          <t>Palier</t>
+        </is>
+      </c>
+      <c r="B10" s="17" t="inlineStr">
+        <is>
+          <t>Seuil prime (%)</t>
+        </is>
+      </c>
+      <c r="C10" s="17" t="inlineStr">
+        <is>
+          <t>Projets clôturés (cumul)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Déclencheur</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>80</v>
+      </c>
+      <c r="C11" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Palier 2</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>90</v>
+      </c>
+      <c r="C12" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>100</v>
+      </c>
+      <c r="C13" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Contexte</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>117 existants au 1er janvier 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="16" t="inlineStr">
+        <is>
+          <t>OBJECTIF SATISFACTION CLIENT (CSAT)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Lien fichier</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>https://sogelink.sharepoint.com/:x:/t/EquipeDeliveryLittralisGeODP-Suividelasatisfactionclient/IQCO8d4z_n7GQLJXQTADrXO3AewqcvG6amiuGealjJiWioI?e=NvUwLm</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>